--- a/players.xlsx
+++ b/players.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rperson/Documents/GitHub/hockey-team-selection/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A79FC922-129C-7E4B-9F39-3ED5E74F7BAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47C0EFD6-9810-394D-9387-3C7CE7DA428B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11000" yWindow="1320" windowWidth="34560" windowHeight="21680" xr2:uid="{8F03AA85-43B9-ED4D-B2F9-79F211193666}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="136">
   <si>
     <t>_x000C_</t>
   </si>
@@ -435,6 +435,12 @@
   </si>
   <si>
     <t>Selected</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -814,7 +820,9 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="2"/>
+      <c r="A2" s="2" t="s">
+        <v>134</v>
+      </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
@@ -826,7 +834,9 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="2"/>
+      <c r="A3" s="2" t="s">
+        <v>135</v>
+      </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
@@ -838,7 +848,9 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="2"/>
+      <c r="A4" s="2" t="s">
+        <v>134</v>
+      </c>
       <c r="B4" s="1" t="s">
         <v>8</v>
       </c>
@@ -850,7 +862,9 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="2"/>
+      <c r="A5" s="2" t="s">
+        <v>135</v>
+      </c>
       <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
@@ -862,7 +876,9 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="2"/>
+      <c r="A6" s="2" t="s">
+        <v>134</v>
+      </c>
       <c r="B6" s="1" t="s">
         <v>10</v>
       </c>
@@ -874,7 +890,9 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="2"/>
+      <c r="A7" s="2" t="s">
+        <v>135</v>
+      </c>
       <c r="B7" s="1" t="s">
         <v>11</v>
       </c>
@@ -886,7 +904,9 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="2"/>
+      <c r="A8" s="2" t="s">
+        <v>134</v>
+      </c>
       <c r="B8" s="1" t="s">
         <v>12</v>
       </c>
@@ -898,7 +918,9 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="2"/>
+      <c r="A9" s="2" t="s">
+        <v>135</v>
+      </c>
       <c r="B9" s="1" t="s">
         <v>13</v>
       </c>
@@ -910,7 +932,9 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="2"/>
+      <c r="A10" s="2" t="s">
+        <v>134</v>
+      </c>
       <c r="B10" s="1" t="s">
         <v>14</v>
       </c>
@@ -922,7 +946,9 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="2"/>
+      <c r="A11" s="2" t="s">
+        <v>135</v>
+      </c>
       <c r="B11" s="1" t="s">
         <v>15</v>
       </c>
@@ -934,7 +960,9 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="2"/>
+      <c r="A12" s="2" t="s">
+        <v>134</v>
+      </c>
       <c r="B12" s="1" t="s">
         <v>16</v>
       </c>
@@ -946,7 +974,9 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="2"/>
+      <c r="A13" s="2" t="s">
+        <v>135</v>
+      </c>
       <c r="B13" s="1" t="s">
         <v>17</v>
       </c>
@@ -958,7 +988,9 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="2"/>
+      <c r="A14" s="2" t="s">
+        <v>134</v>
+      </c>
       <c r="B14" s="1" t="s">
         <v>18</v>
       </c>
@@ -970,7 +1002,9 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="2"/>
+      <c r="A15" s="2" t="s">
+        <v>135</v>
+      </c>
       <c r="B15" s="1" t="s">
         <v>19</v>
       </c>
@@ -982,7 +1016,9 @@
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="2"/>
+      <c r="A16" s="2" t="s">
+        <v>134</v>
+      </c>
       <c r="B16" s="1" t="s">
         <v>20</v>
       </c>
@@ -994,7 +1030,9 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="2"/>
+      <c r="A17" s="2" t="s">
+        <v>135</v>
+      </c>
       <c r="B17" s="1" t="s">
         <v>21</v>
       </c>
@@ -1006,7 +1044,9 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="2"/>
+      <c r="A18" s="2" t="s">
+        <v>134</v>
+      </c>
       <c r="B18" s="1" t="s">
         <v>22</v>
       </c>
@@ -1018,7 +1058,9 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="2"/>
+      <c r="A19" s="2" t="s">
+        <v>135</v>
+      </c>
       <c r="B19" s="2" t="s">
         <v>23</v>
       </c>
@@ -1030,7 +1072,9 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="2"/>
+      <c r="A20" s="2" t="s">
+        <v>134</v>
+      </c>
       <c r="B20" s="2" t="s">
         <v>24</v>
       </c>
@@ -1042,7 +1086,9 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="2"/>
+      <c r="A21" s="2" t="s">
+        <v>135</v>
+      </c>
       <c r="B21" s="2" t="s">
         <v>25</v>
       </c>
@@ -1054,7 +1100,9 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="2"/>
+      <c r="A22" s="2" t="s">
+        <v>134</v>
+      </c>
       <c r="B22" s="2" t="s">
         <v>26</v>
       </c>
@@ -1066,7 +1114,9 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="2"/>
+      <c r="A23" s="2" t="s">
+        <v>135</v>
+      </c>
       <c r="B23" s="2" t="s">
         <v>27</v>
       </c>
@@ -1078,7 +1128,9 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="2"/>
+      <c r="A24" s="2" t="s">
+        <v>134</v>
+      </c>
       <c r="B24" s="2" t="s">
         <v>28</v>
       </c>
@@ -1090,7 +1142,9 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="2"/>
+      <c r="A25" s="2" t="s">
+        <v>135</v>
+      </c>
       <c r="B25" s="2" t="s">
         <v>29</v>
       </c>
@@ -1102,7 +1156,9 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="2"/>
+      <c r="A26" s="2" t="s">
+        <v>134</v>
+      </c>
       <c r="B26" s="2" t="s">
         <v>30</v>
       </c>
@@ -1114,7 +1170,9 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="2"/>
+      <c r="A27" s="2" t="s">
+        <v>135</v>
+      </c>
       <c r="B27" s="2" t="s">
         <v>32</v>
       </c>
@@ -1126,7 +1184,9 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="2"/>
+      <c r="A28" s="2" t="s">
+        <v>134</v>
+      </c>
       <c r="B28" s="2" t="s">
         <v>33</v>
       </c>
@@ -1138,7 +1198,9 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="2"/>
+      <c r="A29" s="2" t="s">
+        <v>135</v>
+      </c>
       <c r="B29" s="2" t="s">
         <v>34</v>
       </c>
@@ -1150,7 +1212,9 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="2"/>
+      <c r="A30" s="2" t="s">
+        <v>134</v>
+      </c>
       <c r="B30" s="2" t="s">
         <v>35</v>
       </c>
@@ -1162,7 +1226,9 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="2"/>
+      <c r="A31" s="2" t="s">
+        <v>135</v>
+      </c>
       <c r="B31" s="2" t="s">
         <v>36</v>
       </c>
@@ -1174,7 +1240,9 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="2"/>
+      <c r="A32" s="2" t="s">
+        <v>134</v>
+      </c>
       <c r="B32" s="2" t="s">
         <v>37</v>
       </c>
@@ -1186,7 +1254,9 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="2"/>
+      <c r="A33" s="2" t="s">
+        <v>135</v>
+      </c>
       <c r="B33" s="2" t="s">
         <v>38</v>
       </c>
@@ -1198,7 +1268,9 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="2"/>
+      <c r="A34" s="2" t="s">
+        <v>134</v>
+      </c>
       <c r="B34" s="2" t="s">
         <v>39</v>
       </c>
@@ -1210,7 +1282,9 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="2"/>
+      <c r="A35" s="2" t="s">
+        <v>135</v>
+      </c>
       <c r="B35" s="2" t="s">
         <v>40</v>
       </c>
@@ -1222,7 +1296,9 @@
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="2"/>
+      <c r="A36" s="2" t="s">
+        <v>134</v>
+      </c>
       <c r="B36" s="2" t="s">
         <v>41</v>
       </c>
